--- a/docs/輪廻の天秤_仕様書_規格書_v0.4.xlsx
+++ b/docs/輪廻の天秤_仕様書_規格書_v0.4.xlsx
@@ -5316,7 +5316,7 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>BGM（12 首）</t>
+          <t>BGM（11 首）</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
